--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="553">
   <si>
     <t>Property</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Timing/process metric profile for door-to-needle, door-to-groin, onset-to-door and related indicators.</t>
+    <t>Observation profile for stroke time metrics and process indicators such as door-to-needle, door-to-groin, onset-to-door and related measures.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -694,7 +694,7 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
+    <t>Procedure or administration measured by this timing metric</t>
   </si>
   <si>
     <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
@@ -715,7 +715,7 @@
     <t>Observation.status</t>
   </si>
   <si>
-    <t>registered | preliminary | final | amended +</t>
+    <t>Final registry observation</t>
   </si>
   <si>
     <t>The status of the result value.</t>
@@ -792,7 +792,7 @@
 </t>
   </si>
   <si>
-    <t>Type of observation (code / type)</t>
+    <t>Timing or process metric</t>
   </si>
   <si>
     <t>Describes what was observed. Sometimes this is called the observation "name".</t>
@@ -833,10 +833,10 @@
 </t>
   </si>
   <si>
-    <t>Who and/or what the observation is about</t>
-  </si>
-  <si>
-    <t>The patient, or group of patients, location, device, organization, procedure or practitioner this observation is about and into whose or what record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>RES-Q registry patient</t>
+  </si>
+  <si>
+    <t>Patient who experienced the index stroke episode represented in this registry dataset.</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated. The subject of an Observation may in some cases be a procedure.  This supports the regulatory inspection use case where observations are captured during inspections of a procedure that is being performed (independent of any particular patient or whether patient related at all).</t>
@@ -887,10 +887,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>Index stroke encounter</t>
+  </si>
+  <si>
+    <t>Encounter that anchors the clinical fact to the acute stroke episode and hospital pathway.</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -1006,7 +1006,7 @@
 boolean</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Metric duration/value or yes/no indicator</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1059,6 +1059,9 @@
 </t>
   </si>
   <si>
+    <t>Actual result</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueQuantity.id</t>
   </si>
   <si>
@@ -1179,6 +1182,9 @@
   </si>
   <si>
     <t>Need to know the system that defines the coded form of the unit.</t>
+  </si>
+  <si>
+    <t>http://unitsofmeasure.org</t>
   </si>
   <si>
     <t>Quantity.system</t>
@@ -1967,98 +1973,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -2252,10 +2260,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2337,7 +2345,7 @@
         <v>82</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>80</v>
@@ -5885,7 +5893,7 @@
         <v>328</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="M32" t="s" s="2">
         <v>316</v>
@@ -5978,10 +5986,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6096,10 +6104,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6169,10 +6177,10 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
@@ -6216,10 +6224,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6242,19 +6250,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
@@ -6303,7 +6311,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6327,10 +6335,10 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
@@ -6338,10 +6346,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6367,20 +6375,20 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="R36" t="s" s="2">
         <v>82</v>
@@ -6404,10 +6412,10 @@
         <v>118</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6425,7 +6433,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6449,10 +6457,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6460,10 +6468,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6489,14 +6497,14 @@
         <v>183</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6545,7 +6553,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6569,10 +6577,10 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
@@ -6580,10 +6588,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6609,21 +6617,21 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>82</v>
@@ -6665,7 +6673,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6674,7 +6682,7 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -6689,10 +6697,10 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>82</v>
@@ -6700,10 +6708,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6729,16 +6737,16 @@
         <v>114</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -6787,7 +6795,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6796,7 +6804,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -6811,10 +6819,10 @@
         <v>82</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AP39" t="s" s="2">
         <v>82</v>
@@ -6822,10 +6830,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6851,16 +6859,16 @@
         <v>235</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6885,13 +6893,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6909,7 +6917,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6918,7 +6926,7 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>106</v>
@@ -6936,7 +6944,7 @@
         <v>139</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6944,14 +6952,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6973,16 +6981,16 @@
         <v>235</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7007,13 +7015,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7031,7 +7039,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7052,24 +7060,24 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7092,19 +7100,19 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7153,7 +7161,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7177,10 +7185,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7188,10 +7196,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7217,13 +7225,13 @@
         <v>235</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7249,13 +7257,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7273,7 +7281,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7282,7 +7290,7 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
@@ -7294,24 +7302,24 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7334,16 +7342,16 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7393,7 +7401,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7402,7 +7410,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7420,7 +7428,7 @@
         <v>82</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7428,10 +7436,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7457,16 +7465,16 @@
         <v>235</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7491,13 +7499,13 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>82</v>
@@ -7515,7 +7523,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7539,10 +7547,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7550,10 +7558,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7576,16 +7584,16 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7635,7 +7643,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7647,7 +7655,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7656,24 +7664,24 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7696,16 +7704,16 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7755,7 +7763,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7776,24 +7784,24 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7819,16 +7827,16 @@
         <v>179</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7877,7 +7885,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7889,7 +7897,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7901,10 +7909,10 @@
         <v>82</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7912,10 +7920,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8030,10 +8038,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8150,10 +8158,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8272,10 +8280,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8298,13 +8306,13 @@
         <v>82</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8355,7 +8363,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8364,7 +8372,7 @@
         <v>94</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8379,10 +8387,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8390,10 +8398,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8416,13 +8424,13 @@
         <v>82</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8473,7 +8481,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8482,7 +8490,7 @@
         <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8497,10 +8505,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8508,10 +8516,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8537,10 +8545,10 @@
         <v>235</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8567,13 +8575,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8591,7 +8599,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8615,10 +8623,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8626,10 +8634,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8655,16 +8663,16 @@
         <v>235</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8692,10 +8700,10 @@
         <v>240</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8713,7 +8721,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8734,13 +8742,13 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8748,10 +8756,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8777,16 +8785,16 @@
         <v>235</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8811,13 +8819,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8835,7 +8843,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8856,13 +8864,13 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8870,10 +8878,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8896,17 +8904,17 @@
         <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8955,7 +8963,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8982,7 +8990,7 @@
         <v>82</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8990,10 +8998,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9016,13 +9024,13 @@
         <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9073,7 +9081,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9082,7 +9090,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9097,10 +9105,10 @@
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9108,10 +9116,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9134,16 +9142,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9193,7 +9201,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9217,7 +9225,7 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>201</v>
@@ -9228,10 +9236,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9254,16 +9262,16 @@
         <v>95</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9313,7 +9321,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9337,10 +9345,10 @@
         <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>82</v>
@@ -9348,10 +9356,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9377,16 +9385,16 @@
         <v>179</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9435,7 +9443,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9459,10 +9467,10 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>82</v>
@@ -9470,10 +9478,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9588,10 +9596,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9708,10 +9716,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9830,10 +9838,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9859,13 +9867,13 @@
         <v>235</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="O65" t="s" s="2">
         <v>250</v>
@@ -9893,13 +9901,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9917,7 +9925,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>94</v>
@@ -9938,7 +9946,7 @@
         <v>254</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>256</v>
@@ -9952,10 +9960,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9978,16 +9986,16 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="M66" t="s" s="2">
         <v>316</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O66" t="s" s="2">
         <v>318</v>
@@ -10039,7 +10047,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10060,7 +10068,7 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>323</v>
@@ -10074,10 +10082,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10103,16 +10111,16 @@
         <v>235</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10137,13 +10145,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10161,7 +10169,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10188,7 +10196,7 @@
         <v>139</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>82</v>
@@ -10196,14 +10204,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10225,16 +10233,16 @@
         <v>235</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10259,13 +10267,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10283,7 +10291,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10304,24 +10312,24 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10347,16 +10355,16 @@
         <v>83</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10405,7 +10413,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10429,10 +10437,10 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>82</v>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1184,7 +1184,7 @@
     <t>Need to know the system that defines the coded form of the unit.</t>
   </si>
   <si>
-    <t>http://unitsofmeasure.org</t>
+    <t>https://ucum.org/ucum</t>
   </si>
   <si>
     <t>Quantity.system</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2678" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1026,13 +1026,6 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>obs-7
 obs-6</t>
   </si>
@@ -1047,178 +1040,6 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.value</t>
-  </si>
-  <si>
-    <t>Observation.value[x].value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decimal
-</t>
-  </si>
-  <si>
-    <t>Numerical value (with implicit precision)</t>
-  </si>
-  <si>
-    <t>The value of the measured amount. The value includes an implicit precision in the presentation of the value.</t>
-  </si>
-  <si>
-    <t>The implicit precision in the value should always be honored. Monetary values have their own rules for handling precision (refer to standard accounting text books).</t>
-  </si>
-  <si>
-    <t>Precision is handled implicitly in almost all cases of measurement.</t>
-  </si>
-  <si>
-    <t>Quantity.value</t>
-  </si>
-  <si>
-    <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.comparator</t>
-  </si>
-  <si>
-    <t>Observation.value[x].comparator</t>
-  </si>
-  <si>
-    <t>&lt; | &lt;= | &gt;= | &gt; | ad - how to understand the value</t>
-  </si>
-  <si>
-    <t>How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
-  </si>
-  <si>
-    <t>Need a framework for handling measures where the value is &lt;5ug/L or &gt;400mg/L due to the limitations of measuring methodology.</t>
-  </si>
-  <si>
-    <t>If there is no comparator, then there is no modification of the value</t>
-  </si>
-  <si>
-    <t>How the Quantity should be understood and represented.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/quantity-comparator|5.0.0</t>
-  </si>
-  <si>
-    <t>Quantity.comparator</t>
-  </si>
-  <si>
-    <t>SN.1  / CQ.1</t>
-  </si>
-  <si>
-    <t>IVL properties</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x].unit</t>
-  </si>
-  <si>
-    <t>Unit representation</t>
-  </si>
-  <si>
-    <t>A human-readable form of the unit.</t>
-  </si>
-  <si>
-    <t>There are many representations for units of measure and in many contexts, particular representations are fixed and required. I.e. mcg for micrograms.</t>
-  </si>
-  <si>
-    <t>Quantity.unit</t>
-  </si>
-  <si>
-    <t>(see OBX.6 etc.) / CQ.2</t>
-  </si>
-  <si>
-    <t>PQ.unit</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x].system</t>
-  </si>
-  <si>
-    <t>System that defines coded unit form</t>
-  </si>
-  <si>
-    <t>The identification of the system that provides the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>Need to know the system that defines the coded form of the unit.</t>
-  </si>
-  <si>
-    <t>https://ucum.org/ucum</t>
-  </si>
-  <si>
-    <t>Quantity.system</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qty-3
-</t>
-  </si>
-  <si>
-    <t>CO.codeSystem, PQ.translation.codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueQuantity.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x].code</t>
-  </si>
-  <si>
-    <t>Coded form of the unit</t>
-  </si>
-  <si>
-    <t>A computer processable form of the unit in some unit representation system.</t>
-  </si>
-  <si>
-    <t>The preferred system is UCUM, but SNOMED CT can also be used (for customary units) or ISO 4217 for currency.  The context of use may additionally require a code from a particular system.</t>
-  </si>
-  <si>
-    <t>Need a computable form of the unit that is fixed across all forms. UCUM provides this for quantities, but SNOMED CT provides many units of interest.</t>
-  </si>
-  <si>
-    <t>Quantity.code</t>
-  </si>
-  <si>
-    <t>PQ.code, MO.currency, PQ.translation.code</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2084,12 +1905,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AP61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.6796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.98046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -2115,7 +1936,7 @@
     <col min="26" max="26" width="59.41796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5740,7 +5561,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>313</v>
       </c>
@@ -5817,14 +5638,16 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>313</v>
@@ -5836,7 +5659,7 @@
         <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>106</v>
@@ -5848,28 +5671,26 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AO31" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AP31" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>325</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>82</v>
       </c>
@@ -5887,22 +5708,22 @@
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -5927,13 +5748,13 @@
         <v>82</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>82</v>
@@ -5951,7 +5772,7 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5960,7 +5781,7 @@
         <v>94</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>106</v>
@@ -5972,35 +5793,35 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>322</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>323</v>
+        <v>139</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>325</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6012,16 +5833,20 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>96</v>
+        <v>235</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>184</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>337</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6045,13 +5870,13 @@
         <v>82</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>82</v>
@@ -6069,19 +5894,19 @@
         <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>186</v>
+        <v>334</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6090,28 +5915,28 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>82</v>
+        <v>343</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>188</v>
+        <v>344</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6130,18 +5955,20 @@
         <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>142</v>
+        <v>347</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>143</v>
+        <v>348</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>190</v>
+        <v>349</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>351</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6177,19 +6004,19 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>334</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>335</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>320</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>191</v>
+        <v>346</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6201,7 +6028,7 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6213,10 +6040,10 @@
         <v>82</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>188</v>
+        <v>353</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6224,10 +6051,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6247,23 +6074,21 @@
         <v>82</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>338</v>
+        <v>235</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>342</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6287,13 +6112,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6311,7 +6136,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6320,7 +6145,7 @@
         <v>94</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>106</v>
@@ -6332,24 +6157,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>344</v>
+        <v>363</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>347</v>
+        <v>366</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6366,30 +6191,28 @@
         <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>114</v>
+        <v>367</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q36" t="s" s="2">
-        <v>351</v>
-      </c>
+      <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6409,13 +6232,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6433,7 +6256,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6442,7 +6265,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>82</v>
+        <v>361</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6457,10 +6280,10 @@
         <v>82</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>82</v>
@@ -6468,10 +6291,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6491,20 +6314,22 @@
         <v>82</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>373</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>374</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6529,13 +6354,13 @@
         <v>82</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>82</v>
+        <v>377</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>82</v>
@@ -6553,7 +6378,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6577,21 +6402,21 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6605,33 +6430,33 @@
         <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>108</v>
+        <v>381</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>82</v>
@@ -6673,7 +6498,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6682,10 +6507,10 @@
         <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>106</v>
+        <v>385</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>82</v>
@@ -6694,24 +6519,24 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>82</v>
+        <v>386</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>82</v>
+        <v>389</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6725,29 +6550,27 @@
         <v>94</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>114</v>
+        <v>391</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>379</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6795,7 +6618,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6804,7 +6627,7 @@
         <v>94</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>372</v>
+        <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>106</v>
@@ -6816,24 +6639,24 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>363</v>
+        <v>396</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6844,7 +6667,7 @@
         <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>82</v>
@@ -6856,19 +6679,19 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>383</v>
+        <v>400</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>384</v>
+        <v>401</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>385</v>
+        <v>402</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -6893,13 +6716,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>389</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -6917,19 +6740,19 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>390</v>
+        <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>106</v>
+        <v>404</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>82</v>
@@ -6941,10 +6764,10 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>139</v>
+        <v>405</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>391</v>
+        <v>406</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>82</v>
@@ -6952,21 +6775,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -6978,20 +6801,16 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>394</v>
+        <v>184</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>397</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7015,13 +6834,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>398</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7039,19 +6858,19 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>392</v>
+        <v>186</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7060,28 +6879,28 @@
         <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>400</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>402</v>
+        <v>188</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7100,20 +6919,18 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>405</v>
+        <v>142</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>406</v>
+        <v>143</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>407</v>
+        <v>190</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7161,7 +6978,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>404</v>
+        <v>191</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7173,7 +6990,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7185,10 +7002,10 @@
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>411</v>
+        <v>188</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>82</v>
@@ -7196,44 +7013,46 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>235</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>194</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>195</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>145</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7257,13 +7076,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7281,19 +7100,19 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>412</v>
+        <v>196</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>419</v>
+        <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7302,24 +7121,24 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>420</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7342,17 +7161,15 @@
         <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>411</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>428</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7401,7 +7218,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7410,7 +7227,7 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>106</v>
@@ -7425,10 +7242,10 @@
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>82</v>
@@ -7436,10 +7253,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7462,20 +7279,16 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>235</v>
+        <v>411</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>433</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7499,31 +7312,31 @@
         <v>82</v>
       </c>
       <c r="X45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7532,7 +7345,7 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
@@ -7547,10 +7360,10 @@
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>436</v>
+        <v>405</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>437</v>
+        <v>419</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>82</v>
@@ -7558,10 +7371,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7584,17 +7397,15 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>439</v>
+        <v>235</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>442</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7619,13 +7430,13 @@
         <v>82</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>82</v>
+        <v>424</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>82</v>
@@ -7643,7 +7454,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7655,7 +7466,7 @@
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>443</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7664,24 +7475,24 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>445</v>
+        <v>405</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7704,18 +7515,20 @@
         <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>449</v>
+        <v>235</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>450</v>
+        <v>427</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>451</v>
+        <v>428</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>430</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
@@ -7739,13 +7552,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7763,7 +7576,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7784,24 +7597,24 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>455</v>
+        <v>344</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>456</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7824,19 +7637,19 @@
         <v>82</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>179</v>
+        <v>235</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
@@ -7861,13 +7674,13 @@
         <v>82</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>82</v>
@@ -7885,7 +7698,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7897,7 +7710,7 @@
         <v>82</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>462</v>
+        <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>82</v>
@@ -7906,13 +7719,13 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>464</v>
+        <v>344</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7920,10 +7733,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>465</v>
+        <v>442</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7946,16 +7759,18 @@
         <v>82</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>183</v>
+        <v>443</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>184</v>
+        <v>444</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>185</v>
+        <v>445</v>
       </c>
       <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
@@ -8003,7 +7818,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>186</v>
+        <v>442</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8012,10 +7827,10 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8030,7 +7845,7 @@
         <v>82</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>188</v>
+        <v>447</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8038,21 +7853,21 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>448</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>82</v>
@@ -8064,17 +7879,15 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>142</v>
+        <v>449</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>143</v>
+        <v>450</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8123,19 +7936,19 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>191</v>
+        <v>448</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>82</v>
+        <v>414</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>82</v>
@@ -8147,10 +7960,10 @@
         <v>82</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>188</v>
+        <v>452</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8158,14 +7971,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8178,26 +7991,24 @@
         <v>82</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>142</v>
+        <v>454</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>194</v>
+        <v>455</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>195</v>
+        <v>456</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8245,7 +8056,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>196</v>
+        <v>453</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8257,7 +8068,7 @@
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>82</v>
@@ -8269,10 +8080,10 @@
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>458</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>139</v>
+        <v>201</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8280,10 +8091,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8294,7 +8105,7 @@
         <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>82</v>
@@ -8303,18 +8114,20 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8363,16 +8176,16 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>106</v>
@@ -8387,10 +8200,10 @@
         <v>82</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>473</v>
+        <v>464</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8398,10 +8211,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8412,7 +8225,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8421,19 +8234,23 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="O53" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="L53" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8481,16 +8298,16 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>472</v>
+        <v>252</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>106</v>
@@ -8505,10 +8322,10 @@
         <v>82</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8516,10 +8333,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8542,13 +8359,13 @@
         <v>82</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>235</v>
+        <v>183</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>479</v>
+        <v>184</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>480</v>
+        <v>185</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8575,13 +8392,13 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>481</v>
+        <v>82</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8599,7 +8416,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>478</v>
+        <v>186</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8608,10 +8425,10 @@
         <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>82</v>
+        <v>187</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
@@ -8623,10 +8440,10 @@
         <v>82</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>463</v>
+        <v>82</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>483</v>
+        <v>188</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8634,21 +8451,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>484</v>
+        <v>473</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8660,20 +8477,18 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>235</v>
+        <v>142</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>485</v>
+        <v>143</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>486</v>
+        <v>190</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>488</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8697,13 +8512,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>489</v>
+        <v>82</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8721,19 +8536,19 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>484</v>
+        <v>191</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>82</v>
@@ -8742,13 +8557,13 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>402</v>
+        <v>188</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
@@ -8756,14 +8571,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8776,25 +8591,25 @@
         <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>235</v>
+        <v>142</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>494</v>
+        <v>194</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>495</v>
+        <v>195</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>496</v>
+        <v>145</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>497</v>
+        <v>151</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -8819,13 +8634,13 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>499</v>
+        <v>82</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8843,7 +8658,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>493</v>
+        <v>196</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8855,7 +8670,7 @@
         <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>82</v>
@@ -8864,13 +8679,13 @@
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>402</v>
+        <v>139</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -8878,10 +8693,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8889,7 +8704,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>94</v>
@@ -8901,20 +8716,22 @@
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>501</v>
+        <v>235</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="O57" t="s" s="2">
-        <v>504</v>
+        <v>250</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
@@ -8939,13 +8756,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>82</v>
+        <v>480</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -8963,16 +8780,16 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>82</v>
+        <v>252</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -8981,16 +8798,16 @@
         <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>481</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>505</v>
+        <v>207</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -8998,10 +8815,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9021,19 +8838,23 @@
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>507</v>
+        <v>483</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>508</v>
+        <v>484</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9081,7 +8902,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>506</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9090,7 +8911,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9102,24 +8923,24 @@
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>486</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>463</v>
+        <v>321</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>510</v>
+        <v>322</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9130,7 +8951,7 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>82</v>
@@ -9139,21 +8960,23 @@
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>512</v>
+        <v>235</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>514</v>
+        <v>489</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9177,13 +9000,13 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>331</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9201,13 +9024,13 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>511</v>
+        <v>487</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>82</v>
@@ -9225,10 +9048,10 @@
         <v>82</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>516</v>
+        <v>139</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>82</v>
@@ -9236,14 +9059,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>82</v>
+        <v>335</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9259,21 +9082,23 @@
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>518</v>
+        <v>235</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>519</v>
+        <v>336</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>520</v>
+        <v>337</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>338</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9297,13 +9122,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>82</v>
+        <v>341</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9321,7 +9146,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9342,24 +9167,24 @@
         <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>342</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>516</v>
+        <v>343</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>522</v>
+        <v>344</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>523</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>523</v>
+        <v>492</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9379,22 +9204,22 @@
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>179</v>
+        <v>83</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>524</v>
+        <v>493</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>525</v>
+        <v>494</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>526</v>
+        <v>402</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>527</v>
+        <v>403</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9443,7 +9268,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>523</v>
+        <v>492</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9452,7 +9277,7 @@
         <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>252</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9467,987 +9292,17 @@
         <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>528</v>
+        <v>405</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>529</v>
+        <v>406</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="62" hidden="true">
-      <c r="A62" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO62" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="63" hidden="true">
-      <c r="A63" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="C63" s="2"/>
-      <c r="D63" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="E63" s="2"/>
-      <c r="F63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K63" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L63" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O63" s="2"/>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" s="2"/>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="AG63" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH63" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ63" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AK63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="64" hidden="true">
-      <c r="A64" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="C64" s="2"/>
-      <c r="D64" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="E64" s="2"/>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q64" s="2"/>
-      <c r="R64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>196</v>
-      </c>
-      <c r="AG64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH64" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ64" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AK64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="65" hidden="true">
-      <c r="A65" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C65" s="2"/>
-      <c r="D65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E65" s="2"/>
-      <c r="F65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q65" s="2"/>
-      <c r="R65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AH65" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI65" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AJ65" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK65" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL65" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="66" hidden="true">
-      <c r="A66" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="C66" s="2"/>
-      <c r="D66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E66" s="2"/>
-      <c r="F66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="P66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q66" s="2"/>
-      <c r="R66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AG66" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH66" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ66" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="67" hidden="true">
-      <c r="A67" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C67" s="2"/>
-      <c r="D67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E67" s="2"/>
-      <c r="F67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G67" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K67" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L67" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q67" s="2"/>
-      <c r="R67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF67" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ67" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="68" hidden="true">
-      <c r="A68" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="C68" s="2"/>
-      <c r="D68" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="E68" s="2"/>
-      <c r="F68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K68" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="L68" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="P68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q68" s="2"/>
-      <c r="R68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X68" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="AG68" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH68" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ68" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL68" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="69" hidden="true">
-      <c r="A69" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="B69" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="C69" s="2"/>
-      <c r="D69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E69" s="2"/>
-      <c r="F69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K69" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L69" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="P69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q69" s="2"/>
-      <c r="R69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ69" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AP69" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP69">
+  <autoFilter ref="A1:AP61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10457,7 +9312,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/timing-metric-observation-profile</t>
+    <t>http://qualityregistry.org/StructureDefinition/timing-metric-observation-profile</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -75,7 +75,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -117,7 +117,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/StructureDefinition/base-stroke-observation</t>
+    <t>http://qualityregistry.org/StructureDefinition/base-stroke-observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -804,7 +804,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/timing-metric-codes-vs</t>
+    <t>http://qualityregistry.org/ValueSet/timing-metric-codes-vs</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -829,7 +829,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/resq-patient-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/resq-patient-profile)
 </t>
   </si>
   <si>
@@ -883,7 +883,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://tecnomod-um.org/StructureDefinition/stroke-encounter-profile)
+    <t xml:space="preserve">Reference(http://qualityregistry.org/StructureDefinition/stroke-encounter-profile)
 </t>
   </si>
   <si>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-timing-metric-observation-profile.xlsx
+++ b/StructureDefinition-timing-metric-observation-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
